--- a/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt1_rubricas.xlsx
@@ -1956,13 +1956,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F844F63-60BD-41F0-B1D1-642DA4669E09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80540073-B321-4B43-8FBB-624152A5BDF0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E48EC18A-32DD-4AD8-BE6E-25CEF782CE85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75771A63-4655-4C94-9AD9-45F545DD21DD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C781BA55-4022-4239-881B-D9C508D1B88D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8570EF4-1BD8-4156-ABB2-87220B0C8DC7}"/>
 </file>